--- a/master lorry.xlsx
+++ b/master lorry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engshengsb-my.sharepoint.com/personal/it2_engsheng_com_my/Documents/Backup/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{E5BD1196-3329-4C57-BF65-31A36F36B3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A570094-943C-46B6-A46B-B3FCBA0910FF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF74F9F-459D-4EFB-823A-40508C5530D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{400969EE-77AD-4116-B449-1FC90F02641B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{400969EE-77AD-4116-B449-1FC90F02641B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="38">
   <si>
     <t>LORRY</t>
   </si>
@@ -147,13 +147,19 @@
   </si>
   <si>
     <t>WYD7184</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Available</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -591,14 +597,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4C2097-FE33-4A35-A59A-3B3AB0EB46A6}">
-  <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -611,8 +619,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -626,8 +637,11 @@
       <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
@@ -641,8 +655,11 @@
       <c r="D3" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -656,8 +673,11 @@
       <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
@@ -671,8 +691,11 @@
       <c r="D5" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
@@ -686,8 +709,11 @@
       <c r="D6" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>10</v>
       </c>
@@ -701,8 +727,11 @@
       <c r="D7" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
@@ -716,8 +745,11 @@
       <c r="D8" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
@@ -731,8 +763,11 @@
       <c r="D9" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
@@ -746,8 +781,11 @@
       <c r="D10" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>14</v>
       </c>
@@ -761,8 +799,11 @@
       <c r="D11" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
@@ -776,8 +817,11 @@
       <c r="D12" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>17</v>
       </c>
@@ -791,8 +835,11 @@
       <c r="D13" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>18</v>
       </c>
@@ -806,8 +853,11 @@
       <c r="D14" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>19</v>
       </c>
@@ -821,8 +871,11 @@
       <c r="D15" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
@@ -836,8 +889,11 @@
       <c r="D16" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>21</v>
       </c>
@@ -851,8 +907,11 @@
       <c r="D17" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>22</v>
       </c>
@@ -866,8 +925,11 @@
       <c r="D18" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>23</v>
       </c>
@@ -881,8 +943,11 @@
       <c r="D19" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>24</v>
       </c>
@@ -896,8 +961,11 @@
       <c r="D20" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>25</v>
       </c>
@@ -911,8 +979,11 @@
       <c r="D21" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>27</v>
       </c>
@@ -926,8 +997,11 @@
       <c r="D22" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>28</v>
       </c>
@@ -941,8 +1015,11 @@
       <c r="D23" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>29</v>
       </c>
@@ -956,8 +1033,11 @@
       <c r="D24" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>30</v>
       </c>
@@ -971,8 +1051,11 @@
       <c r="D25" s="9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>32</v>
       </c>
@@ -986,8 +1069,11 @@
       <c r="D26" s="10" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>34</v>
       </c>
@@ -1001,8 +1087,11 @@
       <c r="D27" s="10" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>35</v>
       </c>
@@ -1016,8 +1105,16 @@
       <c r="D28" s="10" t="s">
         <v>33</v>
       </c>
+      <c r="E28" s="10" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E28" xr:uid="{58B93DB1-8C6E-43BC-8022-F0886421921B}">
+      <formula1>"Available, Block"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>